--- a/results/momentum_failcodes_2026-09-29.xlsx
+++ b/results/momentum_failcodes_2026-09-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A236"/>
+  <dimension ref="A1:A226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,1645 +426,1575 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AERT</t>
+          <t>CHAD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABCL</t>
+          <t>NEON</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ONCO</t>
+          <t>AEHL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACGLO</t>
+          <t>COSM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>ABLV</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABLV</t>
+          <t>AER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RDNW</t>
+          <t>FJDIU</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>ACRV</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>ADI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>AUUD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RFAMU</t>
+          <t>LINK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BLNK</t>
+          <t>AERT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BNKK</t>
+          <t>CAMT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ADAMG</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>AGEN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRKRP</t>
+          <t>QSI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLA</t>
+          <t>AGPU</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>COLA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>SDEV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>AIIA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GGR</t>
+          <t>CRUS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>SXTP</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DOMH</t>
+          <t>ALP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>GCDT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALVO</t>
+          <t>TACH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FAC</t>
+          <t>ARW</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>GNLN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ALZN</t>
+          <t>XRPN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IQST</t>
+          <t>ASBH</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MEDS</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>ASML</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MWC</t>
+          <t>MSS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>ASYS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>MWC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OCC</t>
+          <t>ATEC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NRSN</t>
+          <t>OCC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>ATKR</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QMLS</t>
+          <t>PDC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>ATLCL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>PLAB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>ATLCZ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>POM</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AUC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>RDNW</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PCAP</t>
+          <t>AVAT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>RXT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>AVX</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>SHLS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>SPHL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>BCHT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>BCSS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>BMNP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SONM</t>
+          <t>BNR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BATRA</t>
+          <t>BPRE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WSHP</t>
+          <t>BTCS</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCSS</t>
+          <t>BURU</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BDSX</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BFRG</t>
+          <t>BWMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BHFAL</t>
+          <t>CAI</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>CAN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>CDRO</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>CEVA</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BNGO</t>
+          <t>CHOW</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>CHSCL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CHSCO</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CBAT</t>
+          <t>CLGN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CCNEP</t>
+          <t>CNET</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CNXN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CPIX</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CPOP</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHEC</t>
+          <t>CURX</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHOW</t>
+          <t>DGII</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>DIOD</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>DJCO</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CNTN</t>
+          <t>DJT</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>DXPE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>EDHL</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CPOP</t>
+          <t>EEIQ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>EFSI</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>EGBN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>ENTG</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>EPRX</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CURI</t>
+          <t>FBLA</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CWD</t>
+          <t>FLXS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DJCO</t>
+          <t>FORM</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>FSBW</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>GLND</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>GRI</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>GTBP</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ECX</t>
+          <t>GYRE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EDTK</t>
+          <t>HBIO</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>HITI</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>HQI</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>HSDT</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>IBEX</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>IBRX</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>IFBD</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>INAB</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GEGGL</t>
+          <t>IOND</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>IOSP</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>KAZR</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GLSI</t>
+          <t>KLIC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>KMDA</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GTBP</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GYRE</t>
+          <t>LAUR</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>LTRX</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>MATH</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>MCHPP</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>MRAM</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>MTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>MTLS</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IOND</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>NNBR</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>NTAP</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>NTNX</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>NTRBW</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>NVEC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>NWGL</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>NXXT</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>OLLI</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LTRX</t>
+          <t>ORBS</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>OXBR</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>OXLCZ</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MDWD</t>
+          <t>PAAI</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MIRA</t>
+          <t>PCAP</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>PGEN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>PLXS</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>POWW</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>PSHG</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NSTS</t>
+          <t>PSIG</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>PXLW</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>QNBC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NXXT</t>
+          <t>QRVO</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OCCIN</t>
+          <t>QTRX</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>RCMT</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>RGS</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>RMTI</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OXLCI</t>
+          <t>RUSHB</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>RVSB</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PAAI</t>
+          <t>RWAYL</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PACH</t>
+          <t>RXRX</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>SAFT</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PFLA</t>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PGEN</t>
+          <t>SBMT</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PHOS</t>
+          <t>SGHT</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SHMD</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PLPC</t>
+          <t>SIMO</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SKYA</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SLAB</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PPSI</t>
+          <t>SLMT</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SNPS</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>SONO</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>QNTM</t>
+          <t>SRZN</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SSYS</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>STRC</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>RDIB</t>
+          <t>STRF</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>STRK</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>SUIG</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>SVCO</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>SVIA</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RILYN</t>
+          <t>SVIAW</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>RNW</t>
+          <t>SVRN</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>SWRD</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>TAOX</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>TCPC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>TER</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>TITN</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>TKNO</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SOPH</t>
+          <t>TONX</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SQFTP</t>
+          <t>TWAV</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>VICR</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>WLTH</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>XCBE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>AMPH</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>RENX</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TELO</t>
+          <t>PRTH</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TLACU</t>
+          <t>GRAL</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>YDES</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TONT</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TONX</t>
+          <t>REFR</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TRLV</t>
+          <t>DMAC</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>AIFA</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>XXI</t>
+          <t>AAON</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>PDFS</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>EGHT</t>
+          <t>GGR</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>CRCT</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>LGND</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>SECZ</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>SILC</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>SHPH</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TNMG</t>
+          <t>ARQQ</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>XXI</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>KBSX</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>TAYD</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>MKTW</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>DDOG</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>OESX</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>IMOS</t>
+          <t>WSHP</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MREO</t>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>JWEL</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>ILMN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BHFAM</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ARQQ</t>
+          <t>COHU</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>MREO</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>MLCI</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MRAM</t>
+          <t>CLMB</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>MASS</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BATRK</t>
+          <t>RGEN</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>LSCC</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>BAND</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>KBSX</t>
+          <t>FIRY</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STKE</t>
+          <t>MPWR</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>STKE</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>REFR</t>
+          <t>USDE</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>USDEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>BNR</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>SVCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>SHPH</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>PRTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>TKNO</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>SXTP</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>SUIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>BLLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>FORM</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>EEIQ</t>
+          <t>TJGC</t>
         </is>
       </c>
     </row>
